--- a/InputData/indst/_cement/SYCPbP/Start Year Clinker Production by Pathway.xlsx
+++ b/InputData/indst/_cement/SYCPbP/Start Year Clinker Production by Pathway.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\SYCPbP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07553FE5-8A78-429B-B9B8-C44032D6E306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3F8947-84DC-40DB-BE03-CD7355C289B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -542,19 +542,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="110.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.7265625" customWidth="1"/>
+    <col min="2" max="2" width="110.7265625" customWidth="1"/>
+    <col min="3" max="3" width="3.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -562,67 +562,67 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" s="5">
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="B8" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B11" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B12" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B13" s="5">
         <v>2021</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B14" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="105" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
@@ -630,7 +630,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>30</v>
       </c>
@@ -638,7 +638,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>32</v>
       </c>
@@ -646,7 +646,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>34</v>
       </c>
@@ -665,9 +665,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -678,7 +678,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2021</v>
       </c>
@@ -686,7 +686,7 @@
         <v>79.616</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2022</v>
       </c>
@@ -694,7 +694,7 @@
         <v>79.489000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2023</v>
       </c>
@@ -702,7 +702,7 @@
         <v>76.789000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2024</v>
       </c>
@@ -713,7 +713,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>2025</v>
       </c>
@@ -732,14 +732,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -750,7 +750,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -762,7 +762,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -773,7 +773,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -784,7 +784,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -806,9 +806,9 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -816,7 +816,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -825,7 +825,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -843,7 +843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>17</v>
       </c>

--- a/InputData/indst/_cement/SYCPbP/Start Year Clinker Production by Pathway.xlsx
+++ b/InputData/indst/_cement/SYCPbP/Start Year Clinker Production by Pathway.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\_cement\SYCPbP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF3F8947-84DC-40DB-BE03-CD7355C289B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29E3CD7-1016-4440-A7C8-803F1E89A12B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="12525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="40">
   <si>
     <t>SYCPbP Start Year Clinker Production by Pathway</t>
   </si>
@@ -148,6 +148,15 @@
   </si>
   <si>
     <t>Unit: metric tons clinker/year</t>
+  </si>
+  <si>
+    <t>electric kiln with CCS</t>
+  </si>
+  <si>
+    <t>Electric kiln with CCS</t>
+  </si>
+  <si>
+    <t>The electric kiln with CCS is the electric kiln with a capture unit on its nearly pure CO2 stream, so it uses the electric kiln's value here (same kiln). Its capture is added through CCF (95 percent of calcination CO2 captured) and the CDSC capture inputs.</t>
   </si>
 </sst>
 </file>
@@ -220,7 +229,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -237,6 +246,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -541,20 +556,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.7265625" customWidth="1"/>
-    <col min="2" max="2" width="110.7265625" customWidth="1"/>
-    <col min="3" max="3" width="3.7265625" customWidth="1"/>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="110.7109375" customWidth="1"/>
+    <col min="3" max="3" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -562,67 +577,67 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="5">
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="5">
         <v>2021</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" ht="105" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
@@ -630,7 +645,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>30</v>
       </c>
@@ -638,7 +653,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>32</v>
       </c>
@@ -646,12 +661,20 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -665,9 +688,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -678,7 +701,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2021</v>
       </c>
@@ -686,7 +709,7 @@
         <v>79.616</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2022</v>
       </c>
@@ -694,7 +717,7 @@
         <v>79.489000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2023</v>
       </c>
@@ -702,7 +725,7 @@
         <v>76.789000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2024</v>
       </c>
@@ -713,7 +736,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2025</v>
       </c>
@@ -732,14 +755,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -750,7 +773,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -762,7 +785,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -773,7 +796,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -784,7 +807,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -805,10 +828,10 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>36</v>
       </c>
@@ -816,7 +839,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -825,7 +848,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -834,7 +857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -843,11 +866,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5">
+        <f>B4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>17</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <f>Derivation!B7</f>
         <v>0</v>
       </c>
